--- a/www/download/COUNTRY.AUS.rpO1.xlsx
+++ b/www/download/COUNTRY.AUS.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Austrália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>1.34861762852899</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1.27722079147051</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1.34397767838582</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1.58881470938095</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1.54959474777291</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1.71718034717616</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1.93184453411697</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1.83857323206392</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1.53402461090105</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1.35762575875635</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1.30917466172452</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1.32740422194791</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1.19252052377757</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1.16922821167204</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1.26373683937823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.289</t>
+          <t>2.25757901578717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.355</t>
+          <t>2.16570226527192</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.477</t>
+          <t>2.08536798039144</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.642</t>
+          <t>2.07023426784449</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.834</t>
+          <t>2.16869427869003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.012</t>
+          <t>2.10914134322984</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>2.0330029505631</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.367</t>
+          <t>2.10775848430947</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.519</t>
+          <t>2.22025630388242</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.774</t>
+          <t>2.08789475618108</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.029</t>
+          <t>2.07887907417676</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.288</t>
+          <t>2.01678653035757</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.558</t>
+          <t>1.9479108489885</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10.861</t>
+          <t>1.87305440161396</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10.935</t>
+          <t>1.81328006751808</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.001</t>
+          <t>3.25826079166601</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.121</t>
+          <t>3.16382769578375</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>3.09318257159866</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.404</t>
+          <t>3.10704802683107</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.566</t>
+          <t>3.26715110273724</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.737</t>
+          <t>3.2188352973533</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.864</t>
+          <t>3.13792223222347</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.082</t>
+          <t>3.22172051526841</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>3.36299402901279</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>3.26334560289826</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8.741</t>
+          <t>3.32747271467133</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.965</t>
+          <t>3.23924228422054</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>9.202</t>
+          <t>3.14022033726132</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>9.942</t>
+          <t>3.03806977886596</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10.452</t>
+          <t>2.95543793490168</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15262.516</t>
+          <t>4.41238371342967</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15313.314</t>
+          <t>4.26071902806431</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15492.621</t>
+          <t>4.13697637208657</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15809.188</t>
+          <t>4.12198307133199</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16175.072</t>
+          <t>4.29254907670131</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16516.061</t>
+          <t>4.20878689731965</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16578.653</t>
+          <t>4.08077779766229</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16907.067</t>
+          <t>4.16317600059071</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17174.77</t>
+          <t>4.31001130059648</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17645.28</t>
+          <t>4.1773340261804</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18026.47</t>
+          <t>4.23881964485114</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18424.644</t>
+          <t>4.13383375038341</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18919.606</t>
+          <t>4.01600015476829</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20488.035</t>
+          <t>3.89263780830498</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21545.023</t>
+          <t>3.79244090207236</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12828.687</t>
+          <t>14110760302363.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12974.476</t>
+          <t>13858276655519.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13053.68</t>
+          <t>14322476614930.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13459.16</t>
+          <t>14332920528044.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13759.368</t>
+          <t>16386349687039.1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14064.941</t>
+          <t>17849571217950.1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14063.118</t>
+          <t>17667677581600.9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14373.529</t>
+          <t>19331426451310.9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14680.712</t>
+          <t>23146999761006.9</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15143.81</t>
+          <t>24046743258964.5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15580.662</t>
+          <t>24002647414175.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15917.851</t>
+          <t>22228375421085.1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16341.758</t>
+          <t>20050217623909.3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17671.991</t>
+          <t>16649031266656.7</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>18590.196</t>
+          <t>15885864304010.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>3406692542390.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>3443950853361.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>3502570368453.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>3494712537586.07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>4022014811843.6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>4369572776106.21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>4354272781821.68</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>4643222008313.26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>5628122569122.84</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>5662380104737.83</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>5626936559851.02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>5200732690173.88</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>4695086619007.54</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>3882982962721.37</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>3680980398900.06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>833006501.116931</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>745786818.52123</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>781123896.18257</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>878486887.357163</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>925658198.737621</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>1071013035.9407</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>1121054885.72026</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>1099535210.95153</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>1021753979.75878</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>863408644.617785</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>781630412.519616</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>690872488.934875</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>518719025.722322</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>391480392.066809</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>381713173.846944</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>401584.825321795</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>446706.555377476</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>446424.903972932</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>403043.785411848</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>431842.669543684</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>419315.90099105</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>394027.806547289</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>448561.002070795</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>569687.630994124</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>699358.211433055</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>782122.540424805</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>842370.164041084</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>1024322.7741933</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>1126061.50896517</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>1121941.09699172</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>634372.970973836</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>699783.865357608</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>708031.003611967</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>643013.415336067</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>685252.604319277</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>658162.268161235</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>616008.330882019</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>704703.032197188</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>886591.224382827</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>1107029.17181366</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>1236915.59338804</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>1328732.61972933</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>1598338.88759319</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>1768257.69046221</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>1756569.10439711</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>74031.509210943</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>79198.3107193253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>85099.8371356917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>75727.8216919794</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>81729.8547073177</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>81314.1176749028</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>73193.7582518738</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>76607.355863452</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>90572.4282288111</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>106576.139143213</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>117410.901612856</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>121206.247196359</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>139013.420886207</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>156046.444909782</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>153811.901354841</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.34861762852899</t>
+          <t>486613.707459809</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.27722079147051</t>
+          <t>483646.620233832</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.34397767838582</t>
+          <t>486533.315708779</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.58881470938095</t>
+          <t>471985.783562344</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.54959474777291</t>
+          <t>531593.805652241</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.71718034717616</t>
+          <t>564776.984651913</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93184453411697</t>
+          <t>553688.500366996</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83857323206392</t>
+          <t>574494.796637305</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.53402461090105</t>
+          <t>682064.014834423</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.35762575875635</t>
+          <t>667723.053996294</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.30917466172452</t>
+          <t>643745.153595017</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.32740422194791</t>
+          <t>580117.142164055</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.19252052377757</t>
+          <t>510211.800806056</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.16922821167204</t>
+          <t>390560.301886912</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.26373683937823</t>
+          <t>352186.345849183</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>200929737358.227</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>202198506831.713</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>172646506033.836</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>157700222972.837</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>348790444243.468</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>627161755377.259</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>685769808073.659</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>529135753762.909</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>632135377649.184</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>730265864323.427</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>978380406955.508</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>901793315306.988</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>695870725144.162</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>737188601713.702</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>561057511945.805</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>274986611486.157</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>251520824237.746</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>266639851189.061</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>231433495877.42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>374570687023.788</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>601483493503.535</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>669592154447.464</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>506897285168.379</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>547388817141.048</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>665793046417.098</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>905859036175.139</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>851998345793.025</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>686769889284.134</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>688624959098.145</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>527366651438.349</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>-74056874127.9302</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-49322317406.0326</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-93993345155.2252</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>-73733272904.5826</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>-25780242780.32</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>25678261873.7234</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>16177653626.1947</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>22238468594.5302</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>84746560508.1357</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>64472817906.3291</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>72521370780.3686</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>49794969513.9636</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>9100835860.02884</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>48563642615.5572</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>33690860507.4563</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>2181235.06252922</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>2103612.68796431</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>2061577.10960469</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>1989169.08567575</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>2310907.28973434</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>2407054.73296781</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>2296278.66813543</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>2416400.91912994</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>2949278.83832689</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>2803582.62037824</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>2721222.16350872</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>2403170.44521638</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>2066612.49320686</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>1542617.49974139</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>1361774.812482</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>2173869.2951386</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>2182713.80453565</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>2244939.07742224</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>2214947.37516356</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>2545477.8092456</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>2769724.93088067</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>2742802.43149695</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>2861460.97723267</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>3420963.90837284</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>3401177.3704763</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>3296453.15970817</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>2996523.19748198</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>2657816.4149793</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2146272.79166478</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>2036339.67575562</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>225.76</t>
+          <t>73925.3026335695</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>216.57</t>
+          <t>83143.7064783355</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>208.54</t>
+          <t>85657.6703586451</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>207.02</t>
+          <t>71546.4198589818</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>216.87</t>
+          <t>82657.7304240136</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>210.91</t>
+          <t>90273.7457606642</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>203.3</t>
+          <t>80344.7016223961</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>210.78</t>
+          <t>82430.8733489279</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>222.03</t>
+          <t>95572.9106667517</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>208.79</t>
+          <t>122754.293079389</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>207.89</t>
+          <t>149343.211598088</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>201.68</t>
+          <t>161914.494992754</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>194.79</t>
+          <t>195359.198755723</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>187.31</t>
+          <t>243242.166032765</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>181.33</t>
+          <t>200696.483372384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>325.83</t>
+          <t>2066666947385.4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>316.38</t>
+          <t>2089124418935.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>309.32</t>
+          <t>2222651257701.64</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>310.7</t>
+          <t>2093660977573.67</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>326.72</t>
+          <t>2527021175783.27</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>321.88</t>
+          <t>3035756068339.71</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>313.79</t>
+          <t>2843057359316.16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>322.17</t>
+          <t>2931723514426.17</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>336.3</t>
+          <t>3143874991803.89</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>326.33</t>
+          <t>3292622925597.71</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>332.75</t>
+          <t>3433174303068.77</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>323.92</t>
+          <t>3205202056787.81</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>314.02</t>
+          <t>2922138622075.24</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>303.81</t>
+          <t>2697563709381.02</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>295.54</t>
+          <t>2146346070897.64</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>441.24</t>
+          <t>70489.1347399083</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>426.07</t>
+          <t>76231.1768153268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>413.7</t>
+          <t>82714.6367266814</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>412.2</t>
+          <t>74824.5762535685</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>429.25</t>
+          <t>85369.6177766899</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>420.88</t>
+          <t>83571.7943769528</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>408.08</t>
+          <t>75165.02782931</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>416.32</t>
+          <t>85725.6938519204</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>103238.447633734</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>417.73</t>
+          <t>131595.583649302</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>423.88</t>
+          <t>151441.704391143</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>413.38</t>
+          <t>161775.145211455</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>401.6</t>
+          <t>203614.145602268</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>389.26</t>
+          <t>223979.504872329</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>379.24</t>
+          <t>192821.087558172</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18018811.291</t>
+          <t>2142187057509.82</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18235591.616</t>
+          <t>2066356068441.57</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19030292.436</t>
+          <t>2297189857988.13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19140722.461</t>
+          <t>2374296344419.57</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22485580.047</t>
+          <t>2985310027859.61</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24961210.806</t>
+          <t>3357955972472.87</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25040581.579</t>
+          <t>3275372683433.72</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26803026.979</t>
+          <t>3616293191384.25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>32563575.278</t>
+          <t>4116640547350.68</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>33242241.704</t>
+          <t>4345149474079.26</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>33059719.529</t>
+          <t>4479553873623.65</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>30828593.473</t>
+          <t>4103145693505.5</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>28062294.281</t>
+          <t>3785919886158.93</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>23311125.27</t>
+          <t>3145146308365.86</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>22268231.15</t>
+          <t>2590896407979.41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15270423.144</t>
+          <t>3436.16789366122</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14979405.228</t>
+          <t>6912.52966300878</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14841365.767</t>
+          <t>2943.03363196362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14728354.932</t>
+          <t>-3278.15639458673</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17484220.563</t>
+          <t>-2711.88735267633</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18622927.487</t>
+          <t>6701.95138371143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18058210.885</t>
+          <t>5179.67379308611</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19530004.439</t>
+          <t>-3294.82050299244</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24336282.859</t>
+          <t>-7665.53696698253</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23774752.656</t>
+          <t>-8841.29056991314</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23786034.573</t>
+          <t>-2098.49279305482</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21544350.591</t>
+          <t>139.349781299291</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>19017444.615</t>
+          <t>-8254.9468465452</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>15336831.318</t>
+          <t>19262.6611604358</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14232994.696</t>
+          <t>7875.39581421205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14110760.302</t>
+          <t>-75520110124.4211</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13858276.656</t>
+          <t>22768350493.8373</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14322476.615</t>
+          <t>-74538600286.4854</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14332920.528</t>
+          <t>-280635366845.908</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16386349.687</t>
+          <t>-458288852076.344</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17849571.218</t>
+          <t>-322199904133.165</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17667677.582</t>
+          <t>-432315324117.561</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>19331426.451</t>
+          <t>-684569676958.079</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23146999.761</t>
+          <t>-972765555546.782</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24046743.259</t>
+          <t>-1052526548481.55</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>24002647.414</t>
+          <t>-1046379570554.88</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22228375.421</t>
+          <t>-897943636717.685</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>20050217.624</t>
+          <t>-863781264083.691</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>16649031.267</t>
+          <t>-447582598984.84</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>15885864.304</t>
+          <t>-444550337081.771</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>163327.24381</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>178191.58657</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>177514.85328</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>156770.95752</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>169037.74314</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>161160.70924</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>153651.59963</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>169217.48267</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>218098.91304</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>268298.36943</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>308739.17335</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>326150.75571</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>387434.68136</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>426399.06147</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>431019.08545</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8932705.948</t>
+          <t>0.0370328827118346</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8846421.495</t>
+          <t>0.0412947930615338</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9030551.226</t>
+          <t>0.0428288174215696</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8983940.938</t>
+          <t>0.0444688691063616</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10326593.359</t>
+          <t>0.0484719947053628</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11371981.348</t>
+          <t>0.0456376454920952</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11301074.832</t>
+          <t>0.055740460686857</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>12304933.602</t>
+          <t>0.062690482003955</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14873325.041</t>
+          <t>0.0745508024174448</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>15191367.838</t>
+          <t>0.0785655204106469</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15177277.797</t>
+          <t>0.0846975534192888</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>14092015.182</t>
+          <t>0.0878669519602035</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12849524.403</t>
+          <t>0.0965892638355247</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>10602432.763</t>
+          <t>0.0970063354437479</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>10146486.113</t>
+          <t>0.100361075594903</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>189868.494299314</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>213941.082808452</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>211949.947596942</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>190483.508639969</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>205915.128769095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>197591.943818719</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>184329.016168008</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>204239.350027981</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>260832.844519709</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>317552.901824903</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>354812.091731048</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>383147.040357706</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>462040.19248977</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>511098.123781348</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>498689.56142909</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3406692.542</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3443950.853</t>
+          <t>247042.561166084</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3502570.368</t>
+          <t>245212.233573625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3494712.538</t>
+          <t>218661.70000032</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4022014.812</t>
+          <t>236203.455246225</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4369572.776</t>
+          <t>226529.411581485</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4354272.782</t>
+          <t>211426.463917418</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4643222.008</t>
+          <t>234743.684481662</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5628122.569</t>
+          <t>298459.503014282</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5662380.105</t>
+          <t>362225.598050155</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5626936.56</t>
+          <t>401895.913603307</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5200732.69</t>
+          <t>434454.075255592</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4695086.619</t>
+          <t>525383.13595245</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3882982.963</t>
+          <t>581746.34502725</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3680980.399</t>
+          <t>567463.067505893</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>1538087.02899907</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>1590164.74926371</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>1500355.89328043</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>1283312.26438895</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>1330856.39715423</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>1269664.39282344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>1132604.27923937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>1202551.23465361</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>1469065.97468466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>1726600.80144075</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>1855848.27386571</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>1907051.14573615</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>2169376.54425187</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2388624.46234074</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2294004.94937459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>833.007</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>745.787</t>
+          <t>230599.404506205</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>781.124</t>
+          <t>237949.153674314</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>878.487</t>
+          <t>250262.060632838</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>925.658</t>
+          <t>258406.949753336</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1071.013</t>
+          <t>266933.464059074</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1121.055</t>
+          <t>271889.799504023</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1099.535</t>
+          <t>278369.726039547</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1021.754</t>
+          <t>283092.560448583</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>863.409</t>
+          <t>293634.41830284</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>781.63</t>
+          <t>304609.966543906</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>690.872</t>
+          <t>316215.071145613</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>518.719</t>
+          <t>330465.34834293</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>391.48</t>
+          <t>343645.299165299</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>381.713</t>
+          <t>349635.715183621</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>189868.494299314</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>199357.59835537</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>204863.833201284</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>217116.193006002</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>224556.335046558</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>232338.016803165</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>236773.447442399</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>241378.895999344</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>246305.587297869</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>256072.998226462</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>266920.936391972</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>276821.926296917</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>288651.609567658</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>299855.339807324</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>304287.653401073</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>130991.30575646</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>144863.834973916</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>149358.305756375</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>132795.26679968</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>146239.118943776</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>139258.611128515</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>136325.642552582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>151995.872398338</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>200092.475445718</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>242227.429649845</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>274596.709926693</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>288773.018604408</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>348551.90427755</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>387758.15075275</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>384040.705494107</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15270423144280.5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>14979405228456.3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14841365767243</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>14728354931841.8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17484220563302</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>18622927487486.3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>18058210884843.3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>19530004439180.2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>24336282858513.6</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>23774752656221.2</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>23786034572552.3</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>21544350590767.5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>19017444614570.2</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>15336831317859</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>14232994695963.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>18018811290930.7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>18235591615683.3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19030292435831.4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>19140722461424.1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>22485580047083.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>24961210805579.1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25040581579156.1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>26803026978889.6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>32563575278261.5</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>33242241703672.3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>33059719529315.6</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>30828593472936.8</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>28062294280925.4</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>23311125270352.9</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>22268231150434.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8932705948179.4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8846421494859.22</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9030551225662.13</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8983940937859.16</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10326593358892.6</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11371981348109</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11301074831723.7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12304933602203.5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>14873325040690.5</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>15191367837965.3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>15177277797165.3</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>14092015181835.8</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12849524402568</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10602432763088.6</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>10146486112779.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8288820</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8354550</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8476975</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8641615</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8833540</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9012162.372977</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9129560.80671462</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9366902.84863187</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9518830.40875171</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9773745.40717266</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10028875.8637305</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10288121.0794038</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10558402.0486772</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10861212.6850247</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10935420.7530093</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7000815</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7120800</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7199035</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7404275</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7565955</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7736810.98</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7864119.95</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8082269.91</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8251604.61</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8480132.7</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8740938.13122661</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>8964969.8520771</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>9202230.54737272</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9942083.06364353</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>10451797.5846695</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15262515700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15313313900</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>15492620800</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15809187500</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16175072100</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16516060800</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16578652800</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16907066600</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17174769880</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17645279900</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>18026470142.4781</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>18424644486.6276</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18919606150.8565</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>20488034752.5043</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21545022822.5012</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12828686900</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>12974476100</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13053680400</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13459159500</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>13759368400</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14064941400</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14063117500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14373529200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14680711620</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15143809500</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>15580661526.7842</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>15917851279.2693</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16341757580.232</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17671991252.385</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>18590195705.1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153864968584301</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16029700854778</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166954385727705</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.173855008300376</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.181019712145316</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.188472308501638</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.196239816083751</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.204603232753246</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.210571051646447</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.209717359901643</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.37847368190924</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.378806594382501</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.379326311097916</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.380031673104945</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.380924411145202</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.382009092927736</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.383293158770534</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.381499114359128</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.380542432698167</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.392477390240563</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.439089920935031</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.43232496849829</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.425147874602951</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.41754189002325</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.409484448138053</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.400947169999198</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.391895596574286</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.385326224316197</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.380315087083958</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.369233821286366</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.10955143095146</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.114780512886299</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.120147617578139</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.12567559535655</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.131389805509691</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.137318730790312</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.143494728361388</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.148230307978723</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.151492247330357</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.148429770757862</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.146205954496901</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.348362937765847</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.350930694736798</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.353661187586671</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.356573334821328</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.359688922457053</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.363033185664254</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.366635535000485</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.365531045509784</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.364773902744126</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.37936587381734</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.393915984583342</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.513514202711263</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.505717363805475</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.497619766263762</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.489179641250694</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.480349843461828</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.471076654974004</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.461298308066698</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.457667217940064</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.455162421354089</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.443632926853369</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.431306632348328</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>752494.98168</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>829399.27125</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>832678.26478</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>752129.87266</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>815120.20972</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>781105.49249</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>735918.42278</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>818548.85189</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1043916.75928</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1274561.85401</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1413363.26662</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1511399.28909</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1821221.24465</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2017526.35779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1968895.58857</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>352145.03092</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>391906.39614</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>394570.53933</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>351456.9668</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>382442.57419</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>365788.02271</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>347752.10647</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>386739.55688</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>498551.97846</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>604453.0277</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>676492.62353</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>723227.09386</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>873935.04023</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>969504.49578</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>951503.773</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2074291.31844027</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2058486.2850259</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2058015.25273273</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2067393.1610367</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2094191.92939219</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2109019.69877836</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2139196.35186379</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2199026.60809042</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2286993.16578155</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2403523.49034269</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2553520.13918935</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2731277.7005298</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2980149.29532968</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3230346.10392524</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3478011.97184729</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
